--- a/TABLEUR - GITHUB.xlsx
+++ b/TABLEUR - GITHUB.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthieujacob/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f2daaf98e29d4c7/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A10CF-844F-544C-B7F3-17A246D2FA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
